--- a/Examples/Email Examples - AI Translation.xlsx
+++ b/Examples/Email Examples - AI Translation.xlsx
@@ -1,27 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E539FE08-9BBB-4C8A-A1A8-AF36BDB83A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://laerdal-my.sharepoint.com/personal/gowtham_ravichandran_laerdal_com/Documents/Desktop/email_localization/Examples/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{F2CF1604-2CFE-4B1A-8A0A-5BC2009BA1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2CF7CE2-A6AB-444E-8B22-7B4F57B8E2E9}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="13" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="13" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portuguese" sheetId="6" r:id="rId1"/>
-    <sheet name="Spanish" sheetId="13" r:id="rId2"/>
-    <sheet name="Danish" sheetId="15" r:id="rId3"/>
-    <sheet name="German" sheetId="12" r:id="rId4"/>
-    <sheet name="French" sheetId="11" r:id="rId5"/>
-    <sheet name="Italian" sheetId="10" r:id="rId6"/>
-    <sheet name="Polish" sheetId="9" r:id="rId7"/>
-    <sheet name="Finnish" sheetId="8" r:id="rId8"/>
-    <sheet name="Dutch" sheetId="7" r:id="rId9"/>
-    <sheet name="Swedish" sheetId="5" r:id="rId10"/>
-    <sheet name="Norwegian" sheetId="4" r:id="rId11"/>
-    <sheet name="Korean" sheetId="3" r:id="rId12"/>
-    <sheet name="Japanese" sheetId="2" r:id="rId13"/>
-    <sheet name="Chinese" sheetId="1" r:id="rId14"/>
+    <sheet name="Spanish (Latin America)" sheetId="13" r:id="rId2"/>
+    <sheet name="Spanish (Spain)" sheetId="16" r:id="rId3"/>
+    <sheet name="Danish" sheetId="15" r:id="rId4"/>
+    <sheet name="German" sheetId="12" r:id="rId5"/>
+    <sheet name="French" sheetId="11" r:id="rId6"/>
+    <sheet name="Italian" sheetId="10" r:id="rId7"/>
+    <sheet name="Polish" sheetId="9" r:id="rId8"/>
+    <sheet name="Finnish" sheetId="8" r:id="rId9"/>
+    <sheet name="Dutch" sheetId="7" r:id="rId10"/>
+    <sheet name="Swedish" sheetId="5" r:id="rId11"/>
+    <sheet name="Norwegian" sheetId="4" r:id="rId12"/>
+    <sheet name="Korean" sheetId="3" r:id="rId13"/>
+    <sheet name="Japanese" sheetId="2" r:id="rId14"/>
+    <sheet name="Chinese" sheetId="1" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="305">
   <si>
     <t>Email Example 1</t>
   </si>
@@ -55,6 +61,12 @@
     <t>Email Example 2</t>
   </si>
   <si>
+    <t>Email Example 3</t>
+  </si>
+  <si>
+    <t>Email Example 4</t>
+  </si>
+  <si>
     <t>Subject</t>
   </si>
   <si>
@@ -64,6 +76,12 @@
     <t>Treine sua equipe em atendimento pré-hospitalar (APH), em um ambiente seguro e controlado</t>
   </si>
   <si>
+    <t xml:space="preserve">Participação da Laerdal no IMSH: Visite nosso stand </t>
+  </si>
+  <si>
+    <t>Convite para Você, Colaborador: Festa 20 Anos de Laerdal no Brasil</t>
+  </si>
+  <si>
     <t>Preview Text</t>
   </si>
   <si>
@@ -71,6 +89,12 @@
   </si>
   <si>
     <t>Treine sua equipe com conhecimento e habilidades em atendimento pré-hospitalar (APH), em um ambiente seguro e controlado.</t>
+  </si>
+  <si>
+    <t>Junte-se a nós no IMSH para explorar nossas mais recentes inovações em simulação de saúde.</t>
+  </si>
+  <si>
+    <t>Você é nosso(a) convidado(a) para a Festa de 20 Anos da Laerdal!</t>
   </si>
   <si>
     <t>Title</t>
@@ -83,6 +107,14 @@
   <si>
     <t>Conheça o Similab
 Simulador de ambulância desenvolvido para aprimorar o treinamento em atendimento pré-hospitalar (APH)</t>
+  </si>
+  <si>
+    <t>Queremos te encontrar no IMSH
+10 a 14 de Janeiro | Orlando, Flórida, USA</t>
+  </si>
+  <si>
+    <t>Festa Laerdal 20 Anos
+Dia 2 de junho de 2026, às 19h, em São Paulo.</t>
   </si>
   <si>
     <t>Body</t>
@@ -108,6 +140,26 @@
 Fale com um dos nossos especialistas e descubra como o Similab pode transformar o aprendizado da sua equipe.</t>
   </si>
   <si>
+    <t>Temos o prazer de informar que a Laerdal Medical participará do International Meeting on Simulation in Healthcare (IMSH), um dos eventos mais importantes do mundo focado em simulação na área da saúde. O IMSH reúne profissionais, educadores e líderes do setor para discutir as mais recentes inovações e melhores práticas em simulação, visando melhorar a formação e os resultados no atendimento ao paciente.
+Nosso Vice Presidente da América Latina, Reinaldo Lino, e Victor Espinola, Territory Manager da região do Caribe, estarão no estande da Laerdal recepcionando nossos clientes e contatos do Brasil e América Latina durante o evento.
+Visite o estande da Laerdal Medical (601), para conhecer nossas últimas inovações e soluções que ajudam a:
+Reduzir a mortalidade materna e salvar vidas ao nascimento
+Melhorar o treinamento em equipe e a segurança do paciente
+Gerenciar simulações em larga escala
+Aprimorar a educação baseada em competências
+Transformar o atendimento de emergência
+Esperamos vê-los lá!</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Caro(a)﻿﻿,
+Estamos muito felizes em ter você como nosso(a) convidado(a) especial para um momento marcante da história da Laerdal no Brasil: nossa festa de 20 anos fortalecendo a simulação no nosso país e em toda a América Latina.
+Será um encontro exclusivo, pensado para reunir colaboradores, parceiros e profissionais que desempenham um papel essencial no alcance do nosso propósito: ajudar a salvar vidas.
+Queremos celebrar conquistas, compartilhar experiências e, acima de tudo, valorizar as conexões que tornam nosso trabalho possível.
+Sua presença será muito importante para tornar este momento ainda mais significativo.
+Em breve, compartilharemos mais detalhes.
+</t>
+  </si>
+  <si>
     <t>CTA</t>
   </si>
   <si>
@@ -117,19 +169,34 @@
     <t>Saiba mais</t>
   </si>
   <si>
+    <t>Saiba Mais</t>
+  </si>
+  <si>
+    <t>Confirme sua presença aqui</t>
+  </si>
+  <si>
     <t>Sorpréndase con el NUEVO Harvey® Premier</t>
   </si>
   <si>
     <t>Desbloquea nuevas funciones de la aplicación QCPR sin costo adicional</t>
   </si>
   <si>
-    <t>Translation should be formal for Mexico and Latin America</t>
+    <t>Invitación VIP – 20 años de Laerdal: Una noche especial para celebrar las conexiones que salvan vidas</t>
+  </si>
+  <si>
+    <t>Prepárate para salvar una vida que acaba de empezar.</t>
   </si>
   <si>
     <t>La próxima evolución en el entrenamiento cardiopulmonar ha llegado.</t>
   </si>
   <si>
     <t>Descubre cómo las soluciones QCPR pueden elevar la calidad de tus sesiones de entrenamiento.</t>
+  </si>
+  <si>
+    <t>Es nuestro placer invitarle a la Fiesta de los 20 años de Laerdal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curso de eLearning con acceso a eBook. </t>
   </si>
   <si>
     <t>Harvey® Premier
@@ -137,6 +204,15 @@
   </si>
   <si>
     <t>¿Has explorado las nuevas funciones de la aplicación QCPR?</t>
+  </si>
+  <si>
+    <t>Fiesta Laerdal – 20 años
+2 de junio de 2026, a las 19:00, en São Paulo, Brasil</t>
+  </si>
+  <si>
+    <t>Ya Disponible
+e-NRP 8ª Edición 
+Curso de eLearning con acceso a eBook*</t>
   </si>
   <si>
     <t>​El nuevo Harvey Premier transforma la educación en simulación con su diseño portátil, recursos avanzados de enseñanza remota y una biblioteca de casos ampliada, proporcionando mayor flexibilidad para el entrenamiento en cualquier momento y lugar.
@@ -152,29 +228,151 @@
 Inicia sesión hoy mismo para experimentar las nuevas funciones y aprovechar al máximo tu equipo de Laerdal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Estimado(a)﻿,
+Nos complace contar con su presencia como invitado(a) especial en un momento significativo en la historia de Laerdal en Brasil: la celebración de nuestros 20 años fortaleciendo la simulación en el país y en toda América Latina.
+Será un encuentro exclusivo, concebido para reunir a socios y profesionales que desempeñan un papel esencial en el cumplimiento de nuestro propósito: ayudar a salvar vidas.
+Queremos celebrar logros, compartir experiencias y, sobre todo, valorar las conexiones que hacen posible nuestro trabajo.
+Su presencia será muy importante para hacer de este momento algo aún más significativo.
+En breve compartiremos más detalles.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Neonatal Resuscitation Program® (NRP®) de la American Academy of Pediatrics (AAP) fue creado para abordar la necesidad de realizar un programa educativo que se centra en el manejo inicial de los recién nacidos en sus primeros minutos de vida. A partir de ahora, el curso se encuentra disponible en formato de aprendizaje electrónico. El e-NRP 8.ª edición contiene contenidos para que los proveedores que no tienen acceso a la formación práctica a través de un centro de formación internacional pueden aprender de reanimación neonatal.
+El curso e-NRP consta de tres componentes:
+NRP Básico - Evaluación de Aprendizaje en Línea: cubre los contenidos de las lecciones 1-4 del Libro de texto para la reanimación neonatal
+NRP Avanzado - Evaluación de Aprendizaje en Línea: cubre el contenido de las lecciones 5-11 del Libro de texto para la reanimación neonatal
+Libro de texto para la reanimación neonatal, 8ª Edición [eBook]: acceso en el curso durante dos años después de la activación
+Al completar todas las Ecard del Curso e-NRP 8ª Edición resultan en un Certificado de Finalización del Curso de eLearning.
+</t>
+  </si>
+  <si>
     <t>Descubra lo que hay de nuevo</t>
   </si>
   <si>
     <t>Descubre las novedades</t>
   </si>
   <si>
+    <t>Confirme su asistencia aquí</t>
+  </si>
+  <si>
+    <t>Inscríbete ahora</t>
+  </si>
+  <si>
+    <t>¿Están sus alumnos preparados para la práctica clínica real?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bienvenido a la familia, Paul. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conozca MamaAnne™ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">¡Nuevo Catálogo Laerdal Disponible: Todo en un sólo click! </t>
+  </si>
+  <si>
+    <t>Formar, evaluar y demostrar competencias: el nuevo estándar en FP</t>
+  </si>
+  <si>
+    <t>Nuestro simulador pedriático más reciente</t>
+  </si>
+  <si>
+    <t>Establecer un nuevo estándar en simulación de obstetricia.</t>
+  </si>
+  <si>
+    <t>Nuevas soluciones, misma misión: descubre nuestro nuevo catálogo</t>
+  </si>
+  <si>
+    <t>Mejora la Preparación de tus Alumnos para Salvar Vidas con Formación Práctica en RCP</t>
+  </si>
+  <si>
+    <t>Presentamos a Paul, Nuestro Nuevo Simulador​</t>
+  </si>
+  <si>
+    <t>Conozca MamaAnne™ Simulador de obstetricia</t>
+  </si>
+  <si>
+    <t>¡Innovación, Formación y Soluciones: Accede a nuestro nuevo Catálogo de Productos!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La formación en RCP es una competencia esencial en la FP sanitaria. Contar con herramientas adecuadas permite a los alumnos practicar de forma realista, repetir procedimientos y ganar la confianza necesaria para actuar ante una emergencia.
+Nuestros maniquíes de RCP se adaptan a distintos niveles de aprendizaje, facilitando una formación más eficaz y dinámica que refuerza las habilidades clave desde las primeras prácticas.
+¡Descubre cómo optimizar la formación en RCP en tu centro y mejorar el impacto de cada sesión!.
+Entrena con Confianza.
+Responde con Eficacia. 
+Nuestra amplia gama de productos permite entrenar habilidades clínicas esenciales, desde procedimientos básicos hasta situaciones complejas en el entorno hospitalario. la educación sanitaria está evolucionando hacia modelos como la Educación Basada en Competencias (CBE), orientados a preparar de forma más eficaz a los futuros profesionales. Este enfoque no solo busca la adquisición de conocimientos, sino que pone el énfasis en la aplicación práctica, la toma de decisiones y el desarrollo de habilidades reales.
+</t>
+  </si>
+  <si>
+    <t>Estamos emocionados de anunciar un nuevo y emocionante capítulo en nuestra misión de avanzar en la educación y capacitación médica. Laerdal se ha asociado con SIMCharacters para ofrecerles un simulador innovador y altamente realista para el parto prematuro, Paul. 
+Esto es lo que hace único a Paul:​
+​Realismo: Paul ofrece fisiología y anatomía realistas, mejorando la experiencia de entrenamiento con escenarios auténticos. 
+Características Avanzadas: Equipado con tecnología de vanguardia, Paul simula una amplia gama de condiciones neonatológicas, desde chequeos rutinarios hasta emergencias críticas. 
+Aprendizaje Interactivo: Las características avanzadas de Paul promueven el aprendizaje práctico, el pensamiento crítico y las habilidades de toma de decisiones en un entorno seguro y controlado. 
+Escenarios Personalizables: Personaliza las sesiones de capacitación para satisfacer necesidades educativas específicas, garantizando experiencias de aprendizaje completas y versátiles. 
+Experimenta el realismo de Paul contactando a tu representante local de Laerdal para una demostración.</t>
+  </si>
+  <si>
+    <t>Somos conscientes de la importancia fundamental de fomentar la confianza y la competencia de los profesionales sanitarios a la hora de enfrentarse a emergencias obstétricas. Por eso estamos encantados de presentar MamaAnne, nuestro vanguardista simulador de maternidad y parto, diseñado para revolucionar la formación con simulación de alta fidelidad.
+¿Qué puede esperar de MamaAnne?
+Experiencias realistas: El diseño permite a los alumnos simular escenarios de trabajo de parto y parto inmersivos, preparándolos para manejar emergencias obstétricas críticas con habilidad y precisión.
+Configuración sin esfuerzo: La rápida configuración maximiza el valioso tiempo de formación para crear más oportunidades de aprendizaje práctico.
+Cumpla las normas con facilidad: La alineación con las normas de acreditación y las iniciativas de diversidad, equidad e inclusión hacen de MamaAnne una solución perfecta para cumplir y superar los requisitos de competencia.</t>
+  </si>
+  <si>
+    <t>Nuestra misión es clara: ayudar a salvar un millón de vidas más, cada año, de aquí a 2030.Y la palabra clave es precisamente esa: ayudar.
+Nuestro papel es acompañar y capacitar a quienes están en la primera línea de la atención y la respuesta: desde personas sin formación sanitaria y operadores de centros de emergencias, hasta primeros intervinientes comunitarios y profesionales sanitarios en ambulancias y hospitales.
+Con esta misión en mente, hemos reunido en un único documento todo nuestro portfolio de soluciones, para que puedas encontrar fácilmente la opción que mejor se adapte a tus necesidades de formación.
+Este nuevo catálogo es mucho más que una lista de productos: es una herramienta pensada para apoyar el aprendizaje, mejorar la preparación y contribuir al fortalecimiento de los sistemas de atención y respuesta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explora Nuestros Maniquíes de RCP </t>
+  </si>
+  <si>
+    <t>Explora Paul</t>
+  </si>
+  <si>
+    <t>Conoce a MamaAnne</t>
+  </si>
+  <si>
+    <t>Descarga nuestro catálogo de productos</t>
+  </si>
+  <si>
     <t>Simulationstræning der afspejler fødestuens hverdag – mød MamaAnne</t>
   </si>
   <si>
-    <t>High Emotion Simulation: hvad gør den så effektiv?</t>
+    <t>Invitation til FUN 2026</t>
+  </si>
+  <si>
+    <t>Hukommelse i fokus: Skab læring, der holder</t>
+  </si>
+  <si>
+    <t>Kan simulations-baseret træning hjælpe med tidlig diagnosticering og behandling?</t>
   </si>
   <si>
     <t>MamaAnne® hjælper dig med at undervise i både normale og akutte fødsler – med realistisk udstyr</t>
   </si>
   <si>
-    <t>Oplev, hvordan high emotion simulation med Emma og Emily kan styrke både klinisk præcision og menneskelig forståelse. Læs artiklen og få indblik i, hvorfor det gør en forskel.</t>
+    <t xml:space="preserve">Dansk Førstehjælpsråd og Laerdal byder dig velkommen til årets FUN-møde, som igen afholdes hos Dagrofa Logistik i Vejle.  </t>
+  </si>
+  <si>
+    <t>Få indsigt i, hvordan hukommelsen påvirker læring – og praktiske tips til bedre træning.</t>
+  </si>
+  <si>
+    <t>Træning af sjældne kritiske tilstande</t>
   </si>
   <si>
     <t>MamaAnne® – Træning der redder liv
 inkluderende - virkelighedsnær - effektfuld</t>
   </si>
   <si>
-    <t>Emma og Emily – mere end avanceret neonatal simulation</t>
+    <t>Invitation til FUN 11. juni 2026
+Registrering er åben</t>
+  </si>
+  <si>
+    <t>Hvad du ved, bestemmer, hvad du lærer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Træning af sjældne kritiske tilstande </t>
   </si>
   <si>
     <t xml:space="preserve">Uddannelse og træning i tryg og kompetent fødselshjælp kræver de rette redskaber. MamaAnne® er ét af dem.
@@ -195,34 +393,74 @@
 </t>
   </si>
   <si>
-    <t>Med Emma og Emily har vi taget neonatal træning til et nyt niveau. Disse simulatorer er ikke kun teknisk avancerede – de er designet til at fremkalde realistiske og følelsesmæssigt engagerende scenarier, som styrker både klinisk beslutningstagning og teamwork under pres.
-Ved at integrere High Emotion Simulation bliver træningen mere virkelighedsnær og meningsfuld. Det handler ikke kun om at øve procedurer som thoraxdræn, nåledekompression eller intraossøs adgang – det handler om at træne hele den menneskelige dimension af akut behandling.
-👉 Hvorfor læse artiklen?
-Laerdals artikel om High Emotion Simulation giver dig indsigt i, hvordan følelsesmæssigt engagerende træning kan forbedre læring, fastholde viden og styrke samarbejdet i kritiske situationer. Den viser, hvordan simulatorer som Emma og Emily kan gøre en reel forskel i sundhedsuddannelse og praksis.</t>
+    <t>Dansk Førstehjælpsråd og Laerdal byder dig velkommen til årets FUN-møde, som igen afholdes hos Dagrofa Logistik i Vejle.  
+Implementering af GL2025
+Hvordan omsætter vi de nye guidelines til praksis? Med afsæt i European Resuscitation Council Guidelines 2025 inviterer vi til en faglig dag med fokus på inspiration, refleksion og dialog om fremtidens førstehjælp og genoplivning.
+Programmet er under udvikling, men dagen vil veksle mellem oplæg og workshops og give plads til både overblik, fordybelse og erfaringsudveksling.
+Du kan forvente en dag, hvor vi sammen undersøger, udfordrer og nuancerer implementeringen af guidelines 2025. Fokus er ikke på færdige svar, men på fælles refleksion, faglig inspiration og input, som kan anvendes i undervisning, organisation og praksis.
+Alle med interesse i ovenstående er velkomne og det er som altid gratis at deltage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hvorfor husker man nogle ting – men glemmer andre? Artiklen forklarer, hvordan arbejdshukommelse og langtidshukommelse spiller sammen, hvorfor kognitiv overbelastning opstår, og hvordan skemaer/mentale modeller hjælper os med at fastholde ny viden. Den peger bl.a. på, at arbejdshukommelsen typisk kun kan håndtere 3–5 informationsenheder ad gangen.
+Hvad betyder dette for læring og sammensætning af undervisning.
+Læs artiklen 'Use it or lose it' - om hvordan vores hukommelse fungerer' og få råd til, hvorledes du kan omsætte dette i brug af simulationstræning.
+</t>
+  </si>
+  <si>
+    <t>Kan simulations-baseret træning hjælpe med tidlig diagnosticering og behandling?
+På DASAIM årsmødet 2024 gennemførte Overlæge Kim Zillo Rokamp 4 workshops om identificering og initial behandling af malign hypertermi. Det er en yderst sjælden tilstand, der kan udløses af anæstesi med inhalationsgasser (eksempelvis sevofluran m.fl.) og det muskelrelakserende stof suxamethonium.
+Det kan være vanskeligt at erkende malign hypertermi, og der er ofte flere mulige differentialdiagnoser, men gennem scenarietræningen øves både diagnosticering og iværksættelse af relevant behandling.
+Vil du høre mere om dette scenarie eller anden sparring så tag fat i Iren eller Hans Henrik.</t>
   </si>
   <si>
     <t>Mød MamaAnne</t>
   </si>
   <si>
-    <t>Læs artiklen</t>
+    <t>Info &amp; registrering</t>
+  </si>
+  <si>
+    <t>Læs artiklen her</t>
+  </si>
+  <si>
+    <t>Se vores udvalg af SimMan</t>
   </si>
   <si>
     <t>Probieren Sie SimCapture aus, um Ihr Simulationstraining zu optimieren.</t>
   </si>
   <si>
-    <t>Emily &amp; Emma sind da – realitätsnahe Neugeborenen-Simulation auf höchstem Niveau</t>
+    <t>Ihre exklusive Einladung: Melden Sie sich für das RETTmobil Zirkeltraining 2026 an</t>
+  </si>
+  <si>
+    <t>Neu bei Laparo: Mehr Flexibilität mit Apex PRO BASE</t>
+  </si>
+  <si>
+    <t>Wie die Hochschule Fulda Simulation mit SimCapture neu strukturiert</t>
   </si>
   <si>
     <t>Verbessern Sie Ihr Simulationserlebnis mit einer leistungsstarken Simulationsmanagement-Plattform, die jetzt durch KI ergänzt wurde.</t>
   </si>
   <si>
-    <t>Verbessern Sie die Realitätsnähe und Individualisierbarkeit Ihrer Neugeborenen-Simulationen mit Emily &amp; Emma.</t>
+    <t>Sichern Sie sich als Erste*r einen der streng limitierten Trainingsplätze – nur 2 Teilnehmende pro Session.</t>
+  </si>
+  <si>
+    <t>Modular, skalierbar, budgetfreundlich – das neue Apex PRO BASE.</t>
+  </si>
+  <si>
+    <t>Wie SimCapture die simulationsbasierte Lehre an der Hochschule Fulda unterstützt.</t>
   </si>
   <si>
     <t>Heben Sie Ihre Simulationen mit SimCapture auf die nächste Stufe</t>
   </si>
   <si>
-    <t>Lernen Sie Emily &amp; Emma kennen</t>
+    <t>Geburtshilfe im Rettungsdienst
+Premiere eines lernorientierten Formats auf der diesjährigen RETTmobil</t>
+  </si>
+  <si>
+    <t>Apex PRO wird modular: 
+Mehr Anpassbarkeit, weniger Einstiegsbarrieren</t>
+  </si>
+  <si>
+    <t>Die Erfolgsgeschichte der Hochschule Fulda mit SimCapture</t>
   </si>
   <si>
     <t xml:space="preserve">Möchten Sie die Wirksamkeit Ihrer Schulungen verbessern? SimCapture ist eine leistungsstarke Plattform, die das Simulationsmanagement, die Aufzeichnung, die Nachbesprechung und die Bewertung vereinfacht. Die intuitive Benutzeroberfläche optimiert die Abläufe und sorgt für bessere Ergebnisse sowohl für Lehrkräfte als auch für Teilnehmende – alles an einem Ort.
@@ -237,35 +475,92 @@
 Neu! SimCapture verfügt jetzt über fortschrittliche KI-Technologie und ist damit die ideale Lösung für Simulationen im Gesundheitswesen. Erleben Sie die Vorteile eines optimierten Managements und verbesserter Lernergebnisse für Ihr Team und Ihre Teilnehmenden. </t>
   </si>
   <si>
-    <t>Entdecken Sie Emily und Emma – lebensechte Simulatoren für reife Neugeborene, entwickelt in enger Zusammenarbeit mit Neonatolog:innen, Pflegekräften der Neonatologie und Simulationsexpert:innen. Diese Simulatoren vereinen modernste Technologie mit realistischer Anatomie und ermöglichen ein praxisnahes Training entlang des gesamten neonatologischen Behandlungspfads.
-Was macht Emily &amp; Emma besonders?
-Realitätsnahe Darstellung: Emily (heller Hautton) und Emma (dunkler Hautton) verfügen über naturgetreue Haut, anatomisch korrekte Atemwege basierend auf MRT-Daten sowie flexible Wirbelsäulen für realistische Bewegungsabläufe.
-Training entlang der Versorgungskette: Von der Reanimation bis zur Stabilisierung: Austauschbare Atemwege, pathologische Atemmuster, intraossärer Zugang (Tibia &amp; Femur), zentrale Venenkatheter, PICC-Lines und Kapillarfüllung ermöglichen umfassendes Training in der Neugeborenenversorgung.
-Direktes Feedback: Sensoren erfassen Kopfposition, Tubuslage, Tiefe des UVC, Qualität der Herzdruckmassage und mehr – für sofortiges, verwertbares Feedback im Training.</t>
+    <t xml:space="preserve">In diesem Jahr stellen wir erstmals ein vollständig lernorientiertes Trainingsformat auf der RETTmobil vor. Das Zirkeltraining rückt die Lehre und die praktische Kompetenzentwicklung in den Mittelpunkt – mit einem klaren Fokus auf Geburtshilfe im Rettungsdienst und präklinische Neugeborenenversorgung.
+In 45‑minütigen, zertifizierbaren Trainingseinheiten durchlaufen jeweils zwei Teilnehmende alle Phasen des Lernkreislaufs: strukturierte Wissensaufnahme, gezieltes Skills‑Training, Entscheidungsfindung sowie Simulation in realitätsnaher Umgebung und anschließendes Debriefing. Die Sessions werden von unseren edukativen Experten sowie einer akkreditierten Hebamme begleitet und bieten einen sicheren Rahmen, um Erfahrungen zu sammeln, Methoden anzuwenden und den eigenen Blick auf die Vermittlung kritischer Situationen zu schärfen.
+Für die Premiere dieses neuen Formats steht eine begrenzte Anzahl an Trainings‑Slots zur Verfügung um maximale Trainingsqualität zu gewährleisten. 
+</t>
+  </si>
+  <si>
+    <t>Laparo Medical Simulators ist ein führender Anbieter für Laparoskopie‑Simulation. Als offizieller Vertriebspartner freuen wir uns, eine wichtige Weiterentwicklung des bestehenden Apex‑Portfolios anzukündigen: Apex PRO BASE – eine modulare Grundplattform, die Ausbildungseinrichtungen noch flexibler an ihre Trainingsziele und Budgets anpassen können.
+Der Hintergrund: Trainingszentren arbeiten mit sehr unterschiedlichen Curricula, Lernniveaus und Investitionsplänen. Ein nicht skalierbares, festes Produkt kann diesen Anforderungen immer weniger gerecht werden.
+Mit Apex PRO BASE können Sie mit einer robusten Basiseinheit starten und das System schrittweise erweitern – um zusätzliche Module, Funktionen oder fortgeschrittene Komponenten. Das erleichtert die Budgetplanung, verkürzt Entscheidungsprozesse und senkt Einstiegshürden, ohne die Trainingsqualität zu beeinträchtigen.
+Der modulare Ansatz ermöglicht es Einrichtungen, ihre Simulatorlandschaft strategisch und bedarfsorientiert aufzubauen – phasenweise, transparent und entlang realer Ausbildungsziele.
+Für uns als Vertriebspartner bedeutet das: mehr Flexibilität in der Beratung, zielgerichtete Angebote und eine nachhaltige, wachstumsorientierte Lösung für Ausbildungsprogramme jeder Größe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie lässt sich simulationsbasierte Lehre effizient organisieren, auswerten und weiterentwickeln?
+Die Hochschule Fulda ist ein gutes Beispiel dafür, wie SimCapture dabei unterstützt, Simulationstrainings transparenter zu gestalten, Lernende gezielter zu begleiten und Lehrende in der Planung, Durchführung und Reflexion zu entlasten.
+In der Kundengeschichte erfahren Sie, welche Anforderungen bei der Einführung eine Rolle spielten – von Datenschutz und Projektkoordination bis hin zu Onboarding und Nutzerakzeptanz – und welchen Mehrwert SimCapture heute im SimLab bietet.
+Ein praxisnaher Einblick für alle, die ihre Simulationstrainings strukturierter, skalierbarer und zukunftssicher gestalten möchten.
+</t>
   </si>
   <si>
     <t>Jetzt entdecken</t>
   </si>
   <si>
+    <t>Jetzt Platz sichern</t>
+  </si>
+  <si>
     <t>Mehr erfahren</t>
   </si>
   <si>
+    <t>Kundengeschichte ansehen</t>
+  </si>
+  <si>
+    <t>Inspirez-vous : comment un IFSI a enrichi son offre grâce aux technologies mobiles</t>
+  </si>
+  <si>
     <t>Développer des compétences pratiques pour soutenir le parcours de soins</t>
   </si>
   <si>
     <t>Formation néonatale avancée avec Emily &amp; Emma</t>
   </si>
   <si>
+    <t xml:space="preserve">Soins mère-enfant , vous faites la différence ! </t>
+  </si>
+  <si>
+    <t>Une success story qui montre comment aller encore plus loin dans l’innovation pédagogique.</t>
+  </si>
+  <si>
     <t>Une formation de qualité et réaliste favorise la croissance, la confiance et la préparation.</t>
   </si>
   <si>
     <t>Préparez votre équipe grâce à une formation conçue par des experts pour faire face à chaque urgence néonatale.</t>
   </si>
   <si>
+    <t xml:space="preserve">Chacun d'entre nous est lié à une communauté qui, dans le monde entier, se consacre à promouvoir la santé, le bien-être et à sauver des vies. </t>
+  </si>
+  <si>
+    <t>Diversification de l’offre de simulation santé au moyen de nouvelles technologies mobiles</t>
+  </si>
+  <si>
     <t>Une formation efficace commence par une pratique réaliste</t>
   </si>
   <si>
     <t>Parce que chaque naissance mérite les meilleurs soins.</t>
+  </si>
+  <si>
+    <t>Vous faites la différence !</t>
+  </si>
+  <si>
+    <t>Bonjour,
+En tant qu’IFSI déjà avancé dans vos pratiques de simulation, vous faites partie des établissements qui façonnent la pédagogie de demain.
+Pour continuer à soutenir votre dynamique d’innovation, nous souhaitions partager avec vous une success story inspirante : la diversification d’un centre de formation grâce à l’intégration de technologies mobiles de simulation.
+Comment un institut a élargi son offre pédagogique, renforcé l’autonomie des apprenants et déployé une simulation plus flexible, plus accessible et plus collaborative ?
+Pourquoi cette success story pourrait vous intéresser :
+Vous explorez de nouvelles façons d’intégrer la simulation dans l’ensemble du parcours étudiant
+Vous cherchez à développer la pratique autonome ou “self‑recording”
+Vous souhaitez diversifier les modalités pédagogiques tout en optimisant le temps formateur
+Vous réfléchissez à l’intégration de solutions mobiles pour compléter vos dispositifs existants
+Et si vous alliez encore plus loin ?
+Nos équipes peuvent vous accompagner pour :
+Identifier les axes d’évolution de votre programme de simulation,
+Vous présenter des démonstrations sur les solutions mobiles,
+Vous partager des retours d’expérience concrets d’autres centres avancés.
+N’hésitez pas à revenir vers nous pour organiser un échange personnalisé.
+Au plaisir de continuer à faire évoluer ensemble la simulation au sein de votre IFSI.
+Bien cordialement,
+L’équipe Laerdal Medical France</t>
   </si>
   <si>
     <t>Des soins de qualité commencent bien avant la rencontre avec un patient.
@@ -279,28 +574,60 @@
 Les plus petits patients ont besoin d’aide dans leurs moments les plus vulnérables. Donnez à vos équipes les moyens d’offrir, en toute confiance, le soutien dont elles sont capables.</t>
   </si>
   <si>
+    <t xml:space="preserve">Chacun d'entre nous est lié à une communauté qui, dans le monde entier, se consacre à promouvoir la santé, le bien-être et à sauver des vies. 
+Votre établissement a fait l'acquisition d'un simulateur d'accouchement qui a automatiquement déclenché un don dans le cadre du programme "Un acheté, un offert" de Laerdal.
+« Un acheté, un offert » est un programme conjoint de Laerdal Global Health et Laerdal Medical qui permet de distribuer des simulateurs d'accouchement dans des territoires à faibles revenus. Pour chaque simulateur MamaAnne, SimMom, MamaBirthie ou MamaNatalie acheté dans un pays à revenu élevé, un MamaBirthie ou un MamaNatalie est offert dans le cadre d'un programme partenaire choisi au sein d'un territoire défavorisé.
+De ce fait, vous avez aidé les infirmières, les soignants et les sages-femmes qui portent les mêmes valeurs que vous, mais ne bénéficient pas des mêmes ressources.
+Grâce à vous, l'avenir devient plus prometteur pour les mères et les bébés du monde entier ! </t>
+  </si>
+  <si>
+    <t>Lire l'article</t>
+  </si>
+  <si>
     <t>Découvrez les Skills Trainers Laerdal</t>
   </si>
   <si>
     <t>Formation néonatale avancée</t>
   </si>
   <si>
+    <t xml:space="preserve">En savoir plus </t>
+  </si>
+  <si>
     <t>Presentazione delle nuove funzionalità della nostra app QCPR</t>
   </si>
   <si>
     <t>Formazione avanzata in neonatologia con Emily ed Emma</t>
   </si>
   <si>
+    <t xml:space="preserve">Una nuova era nella cura neonatale: scoprite NeoBeat </t>
+  </si>
+  <si>
+    <t>Vi presentiamo KnowledgeHub.</t>
+  </si>
+  <si>
     <t>La nostra soluzione QCPR è appena migliorata con la nuova versione pro</t>
   </si>
   <si>
     <t xml:space="preserve">Prepara il tuo team con una formazione progettata da esperti per ogni emergenza neonatale. </t>
   </si>
   <si>
+    <t xml:space="preserve">Rapido, accurato, oggettivo: NeoBeat è arrivato </t>
+  </si>
+  <si>
+    <t>Tutte le risorse in un unico posto.</t>
+  </si>
+  <si>
     <t>La nostra soluzione QCPR è ora più potente che mai</t>
   </si>
   <si>
     <t>Ogni dono prezioso merita cure esperte</t>
+  </si>
+  <si>
+    <t>Vi presentiamo NeoBeat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vi presentiamo KnowledgeHub
+Competenze senza Limiti </t>
   </si>
   <si>
     <t>Siamo lieti di annunciare che la soluzione QCPR di Laerdal è stata ulteriormente migliorata con il rilascio delle funzionalità pro dell'app QCPR. Ora potete accedere a nuove potenti funzionalità senza costi aggiuntivi.
@@ -318,22 +645,52 @@
 I pazienti più piccoli hanno bisogno di aiuto nei momenti più vulnerabili. Consenti ai tuoi team di fornire con sicurezza il supporto eccezionale di cui sono capaci.</t>
   </si>
   <si>
+    <t xml:space="preserve">NeoBeat sta rivoluzionando la valutazione della frequenza cardiaca neonatale, fornendo letture accurate in tempo reale. 
+Progettato per l'uso durante la rianimazione neonatale, NeoBeat fornisce la frequenza cardiaca in tempo reale basata sull'ECG utilizzando elettrodi a secco, senza adesivi, senza cavi e senza necessità di asciugare il bambino.
+Quando viene posizionato sul torace del neonato, NeoBeat presenta la frequenza cardiaca in modo rapido e oggettivo, consentendo agli operatori sanitari di concentrarsi sul bambino quando ogni secondo è prezioso. 
+Vieni a trovarci alla SIN 7-8 Ottobre stand n. 25, avrai occasione di provarlo con le tue mani. </t>
+  </si>
+  <si>
+    <t>Laerdal KnowledgeHub è una biblioteca digitale in cui le organizzazioni troveranno tutte le risorse necessarie per imparare le basi e ottenere il massimo dalle apparecchiature di simulazione. Pensato per le routine più impegnative, KnowledgeHub offre un accesso illimitato agli ausili per la formazione e agli strumenti per la manutenzione, consentendo ai membri del team di acquisire le competenze necessarie per ottimizzare le prestazioni dei corsi di simulazione.
+Rafforzare le competenze di simulazione con contenuti affidabili
+Sviluppare, trattenere e far progredire il personale di simulazione e i docenti di talento
+Ridurre i costi di formazione e manutenzione senza sacrificare la qualità</t>
+  </si>
+  <si>
     <t>Scorpi la novità</t>
   </si>
   <si>
     <t>Training Neonatale Avanzato</t>
   </si>
   <si>
+    <t>Clicca per saperne di più</t>
+  </si>
+  <si>
+    <t>Scopri di più</t>
+  </si>
+  <si>
     <t>Fantom do badania fizykalnego - CaRE</t>
   </si>
   <si>
     <t>Poznaj Emily i Emmę</t>
   </si>
   <si>
+    <t>Twój medyczny świat online - odkryj go z naszym nowym sklepem internetowym!</t>
+  </si>
+  <si>
+    <t>Perfekcyjne RKO za każdym razem</t>
+  </si>
+  <si>
     <t>Rozwijaj kompetencje z zakresu identyfikacji pulsu, rozpoznania tonów serca i szmerów oddechowych</t>
   </si>
   <si>
     <t>Większy realizm i elastyczność w symulacjach neonatologicznych dzięki Emily i Emmie</t>
+  </si>
+  <si>
+    <t>Wysokiej jakości sprzęt bezpośrednio od producenta, teraz dostępny on-line</t>
+  </si>
+  <si>
+    <t>W każdej akcji liczy się jakość RKO. Sprawdź, jak możesz ją kontrolować z pomocą CPRmeter™ 2.</t>
   </si>
   <si>
     <t>Doskonal umiejętności diagnostyczne z CaRE</t>
@@ -341,6 +698,9 @@
   <si>
     <t>Nowe dzieci w rodzinie Laerdal: 
 Emily i Emma</t>
+  </si>
+  <si>
+    <t>Sprzęt medyczny na wyciągnięcie ręki</t>
   </si>
   <si>
     <t>Fantom do badania fizykalnego CaRE umożliwia rozwój kompetencji w zakresie identyfikacji, diagnozowania schorzeń, patologii układu oddechowego i krążenia. Symuluj poszczególne symptomy lub przypadki kliniczne przy użyciu unikalnej technologii, która zapewnia synchronizację pulsu, tonów serca, dzwięków płuc i z ust, z ruchem klatki piersiowej.
@@ -359,28 +719,76 @@
 Natychmiastowa informacja zwrotna: Czujniki monitorują m.in. odchylenie głowy, pozycję rurki dotchawiczej, głębokość wprowadzenia cewnika pępkowego (UVC), jakość RKO i inne parametry — dając szybkie i praktyczne informacje zwrotne dla uczestników szkolenia.</t>
   </si>
   <si>
+    <t xml:space="preserve">Czy wiesz, że...
+Poprzez naszą stronę internetową  możesz teraz zamówić szeroki wybór wysokiej jakości sprzętu medycznego. Wystarczy, że klikniesz na przycisk SKLEP zamieszczony w prawym górnym rogu strony produktowej lub wejdziesz na sklep.laerdal.com
+Produkty dostępne w sklepie, które mogą Cię zainteresować:
+Thomas Select Tube Holder
+Uchwyt rurki intubacyjnej Thomas Select Tube Holder zabezpiecza specjalistyczne urządzenia do udrażniania dróg oddechowych, takie jak rurki dotchawicze lub nadgłośniowe urządzenia do udrażniania dróg oddechowych, zmniejszając ryzyko przypadkowej ekstubacji.
+The BAG II
+Jednorazowy resuscytator BAG II to wysokiej jakości worek samorozprężalny przeznaczony dla pacjentów wymagających całkowitego lub czasowego wspomagania oddechu. Jego ergonomiczna konstrukcja umożliwia dobre wyczucie naturalnego oporu płuc, przezroczysta maska umożliwia obserwowanie koloru skóry pacjenta, a regulowany pasek ułatwia trzymanie zmniejszając zmęczenie dłoni podczas wentylacji. Dostępny w rozmiarach dla dorosłych, dzieci i niemowląt.
+Stifneck Select Collar
+Kołnierz Stifneck Select firmy Laerdal to połączenie czterech kołnierzy o różnych rozmiarach w jednym, łatwym w obsłudze i niezwykle skutecznym rozwiązaniu. Prawidłowo i łatwo stabilizuje pacjentów z urazami kręgosłupa dzięki możliwości regulacji rozmiaru kołnierza, który szybko i bezpiecznie blokuje się w wybranej pozycji (4 różne opcje). Dostępny w rozmiarach dla dorosłych oraz dzieci.
+</t>
+  </si>
+  <si>
+    <t>Jest wiele czynników, które zwiększają szansę przeżycia po zatrzymaniu krążenia, ale żaden nie jest tak istotny jak natychmiastowe rozpoczęcie wysokiej jakości RKO*. Znasz korzyści płynące z bieżącej informacji zwrotnej otrzymywanej podczas szkoleń z RKO, ale skąd wiesz, czy Ty i/lub Twój zespół konsekwentnie dostarczacie wysokiej jakości uciśnięcia, gdy ma to największe znaczenie? 
+Badania pokazują, że sztywność klatki piersiowej pacjenta i odpowiadająca jej siła wymagana do ucisku o głębokości zgodnej z wytycznymi mogą się znacznie różnić w zależności od wielu czynników**, w tym:
+Płci
+Wieku
+Liczby już wykonanych uciśnięć
+Ciężko jest przygotować się do różnych wariacji sztywności klatki piersiowej, dlatego nawet doskonale przeszkolone osoby mogą nie być pewne, czy wykonują uciśnięcia prawidłowo.
+CPRmeter 2 to niewielkie i łatwe w obsłudze asystent RKO, pomagający zoptymalizować wykonanie RKO dzięki przekazywaniu informacji zwrotnych na temat najistotniejszych parametrów resuscytacji w czasie rzeczywistym.</t>
+  </si>
+  <si>
     <t>Dowiedz się więcej o CaRE</t>
   </si>
   <si>
     <t>Dowiedz się więcej</t>
   </si>
   <si>
+    <t>Zobacz ofertę</t>
+  </si>
+  <si>
+    <t>Poznaj CPRmeter 2</t>
+  </si>
+  <si>
     <t>Laadukkaat terveydenhuollon koulutuspaketit Laerdal.com-verkkokaupassa</t>
   </si>
   <si>
     <t>Saat eksklusiivisen katsauksen Emilyyn ja Emmaan - katso video nyt</t>
   </si>
   <si>
+    <t>[Kutsu] Nordic SUN 2026 -tapahtumaan</t>
+  </si>
+  <si>
+    <t>[Save the Date] SimCapture-käyttäjätapaaminen 20.-21.8.2025</t>
+  </si>
+  <si>
     <t>Harjoittele ratkaisuilla, jotka on suunniteltu tukemaan kliinisten taitojen hallintaa.</t>
   </si>
   <si>
     <t>Katso, miten Emily ja Emma asettavat uuden tason simulaatioharjoitteluun.</t>
   </si>
   <si>
+    <t>Nordic SUN 2026 -tapahtuma 3.-4.11. Kööpenhaminassa</t>
+  </si>
+  <si>
+    <t>Varaathan ajan kalenteristasi SimCapture-käyttäjätapaamista varten.</t>
+  </si>
+  <si>
     <t>Käytännön koulutuspaketit päivittäiseen harjoitteluun​</t>
   </si>
   <si>
     <t>Esittelyssä Emily ja Emma ​</t>
+  </si>
+  <si>
+    <t>Kutsu
+Healthcare Simulation User Network
+Opi, jaa ja inspiroidu yhdessä</t>
+  </si>
+  <si>
+    <t>Save the Date!
+SimCapture-käyttäjätapaaminen 2025</t>
   </si>
   <si>
     <t>Elvytys- ja kliinisten taitojen harjoitteluun kootut koulutuspaketit on suunniteltu tukemaan päivittäistä, käytännönläheistä oppimista. Jokainen koulutuspaketti sisältää olennaiset tarvikkeet - kuten elvytysnuket, toimenpidemallit ja hengitysteiden hallinnan välineet - jotka on suunniteltu edistämään johdonmukaista ja taitopainotteista harjoittelua kaikissa koulutusohjelmissasi.
@@ -394,28 +802,77 @@
 Kiinnostaako sinua nähdä, mitä kaikkia ominaisuuksia Emilyllä ja Emmalla on?</t>
   </si>
   <si>
+    <t xml:space="preserve">Tänä vuonna Nordic SUN keskittyy erityisesti terveydenhuollon laadunparannukseen. Tarkastelemme yhdessä, miten simulaatiota voidaan hyödyntää vaikuttavana keinona parantaa hoidon laatua ja potilasturvallisuutta. Yhteisten kokemusten, esitysten, työpajojen ja keskusteluiden kautta syvennymme siihen, miten simulaatio tukee mitattavaa kehitystä, toiminnan yhtenäisyyttä ja kestävää muutosta kliinisessä työssä ja koulutuksessa.
+Järjestämme kaksipäiväisen tapahtuman yhteistyössä Københavns Professionshøjskolen kanssa Kööpenhaminassa.
+Ohjelma
+Sisältää luentoja ja työpajoja
+Ilmoittautumisen yhteydessä valitset 8 vaihtoehdosta 5 työpajaa, joihin osallistut Työpajapaikkoja on rajoitetusti. Lisätiedot työpajoista löytyvät kutsun Agenda-osiosta
+Suomelle tapahtumaan on varattu enintään 30 osallistujapaikkaa
+Osallistuminen
+Osallistumismaksu on 80 €/hlö (sisältää 3.11. illallisen)
+Lasku lähetetään organisaatiolle 3 viikkoa ennen tapahtumaa
+Matka- ja majoituskulut osallistujan vastuulla  
+Majoitus
+Olemme tehneet ennakkovarauksia useisiin hotelleihin Kööpenhaminan keskustassa lähellä 3.11. illallispaikkaa. Tarkemmat tiedot löytyvät kutsulinkistä.
+Kysyttävää
+Kaikissa tapahtumaan liittyvissä asioissa voit olla yhteydessä Laerdal Medical Suomen tiimiin: Johanna Herrala, Juha-Pekka Laakso, Virpi Mannermaa &amp; asiakaspalvelu
+Odotamme innolla kahta inspiroivaa päivää yhdessä kanssasi.
+Ystävällisin terveisin
+Københavns Professionshøjskole &amp; Laerdal Medical Nordic
+</t>
+  </si>
+  <si>
+    <t>Tervetuloa osallistumaan SimCapture-käyttäjätapaamiseen, joka järjestetään Ammattikorkeakoulu Arcadassa, Helsingissä 20.-21.8.2025.
+Tapahtuma tarjoaa erinomaisen tilaisuuden verkostoitua, jakaa kokemuksia ja oppia uutta terveydenhuollon simulaatiopohjaisen koulutuksen tallentamiseen ja hallintaan suunnitellun SimCapture-järjestelmän käytöstä. 
+Lisätietoja ilmoittautumislinkin kera seuraa myöhemmin keväällä. Merkitsethän päivämäärät muistiin kalenteriisi jo nyt!</t>
+  </si>
+  <si>
     <t>Tutustu eri koulutuspaketteihin</t>
   </si>
   <si>
     <t>Katso esittelyvideo</t>
   </si>
   <si>
+    <t>Kutsu - ohjelma - ilmoittautuminen</t>
+  </si>
+  <si>
+    <t>Tietoa SimCapturesta löytyy täältä</t>
+  </si>
+  <si>
     <t>Meer uit de QCPR-app - zonder extra kosten</t>
   </si>
   <si>
     <t>MamaAnne® wint de 2025 iF Design Award​​</t>
   </si>
   <si>
+    <t>Digitale demo volgen? Kies uw moment en oplossing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Familie-uitbreiding! Welkom, Paul. </t>
+  </si>
+  <si>
     <t>Ontdek hoe QCPR uw trainingen slimmer en effectiever maakt.</t>
   </si>
   <si>
     <t>Erkend voor innovatie, realisme en impact in verloskundige simulaties.</t>
   </si>
   <si>
+    <t>Wilt u weten hoe simulatie uw team kan versterken – zonder dat u tijd verliest aan verplaatsingen of installaties?</t>
+  </si>
+  <si>
+    <t>Maak kennis met Paul, onze kleinste simulator.</t>
+  </si>
+  <si>
     <t>Heeft u de nieuwe functies in de QCPR-app al ontdekt?</t>
   </si>
   <si>
     <t>Bekroond ontwerp. Echte impact.</t>
+  </si>
+  <si>
+    <t>Slim trainen begint bij slim kennismaken</t>
+  </si>
+  <si>
+    <t>Maak kennis met Paul, onze kleinste simulator​</t>
   </si>
   <si>
     <t>De nieuwste functies in de QCPR-app zijn nu beschikbaar en klaar voor gebruik met uw Laerdal-oefenpoppen. Geen extra kosten. Wel extra mogelijkheden.
@@ -437,28 +894,72 @@
 Deze award herinnert ons eraan hoe krachtig simulatie kan zijn wanneer ze de patiënten weerspiegelt die we verzorgen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Wilt u weten hoe simulatie uw team kan versterken – zonder dat u tijd verliest aan verplaatsingen of installaties?
+Laerdal biedt nu digitale demo’s aan die u volgt vanop uw eigen werkplek, op een moment dat u past.
+Wat levert het u op?
+Een heldere inkijk in de mogelijkheden van onze simulators
+Interactieve sessie met ruimte voor vragen
+Tijdbesparing voor u én uw collega’s
+Geen installatie of voorbereiding nodig
+Klaar om de mogelijkheden te ontdekken?
+</t>
+  </si>
+  <si>
+    <t>We zijn blij om een spannend nieuw hoofdstuk in onze missie voor medische opleiding en training met u te delen. Laerdal en SIMCharacters stellen u graag de innovatieve en realistische prematuursimulator - Paul - voor.​
+Dit maakt Paul uniek:​
+​Realistisch: Paul heeft een levensechte fysiologie en anatomie, waardoor realistische scenario’s de trainingservaring verrijken.​
+Geavanceerde functies: Met moderne technologie simuleert Paul een breed scala aan neonatologische aandoeningen, van routinecontroles tot kritieke noodsituaties.
+Interactief leren: De geavanceerde functies van Paul bevorderen praktisch leren, kritisch denken en besluitvorming in een veilige en gecontroleerde omgeving.​
+Aanpasbare scenario's: Maak trainingssessies op maat van uw specifieke leerbehoeften, en zorg voor uitgebreide en veelzijdige leerervaringen.</t>
+  </si>
+  <si>
     <t>Ontdek de nieuwe functies</t>
   </si>
   <si>
     <t>Beter ontwerp. Betere training.</t>
   </si>
   <si>
+    <t>Ontdek de digitale demo's</t>
+  </si>
+  <si>
+    <t>Ontdek Paul</t>
+  </si>
+  <si>
     <t>Färdighetstränare: Självförtroende genom upprepad träning</t>
   </si>
   <si>
     <t>Möt Emily and Emma</t>
   </si>
   <si>
+    <t>[Inbjudan] Nordic SUN 2026</t>
+  </si>
+  <si>
+    <t>[Webinar] Lär dig hur du kan få ut mer av SimCapture!</t>
+  </si>
+  <si>
     <t>Allt du behöver för din färdighetsträning</t>
   </si>
   <si>
     <t>Förbättra realismen och anpassa neonatal simuleringar med Emily och Emma</t>
   </si>
   <si>
+    <t>Välkommen till Nordic SUN 2026 i Köpenhamn den 3–4 november</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lär dig mer om hur du kan få ut mer av SimCapture! </t>
+  </si>
+  <si>
     <t>Trygg träning för säkrare vård</t>
   </si>
   <si>
     <t>Emily och Emma är här</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inbjudan Nordic SUN </t>
+  </si>
+  <si>
+    <t>Lär dig hur du kan få ut mer av SimCapture!
+Gratis Webinar | 29. februari 2024 | kl. 14.30-15.30</t>
   </si>
   <si>
     <t>Praktisk träning spelar en viktig roll i utvecklingen av klinisk kompetens. Våra färdighetstränare gör det möjligt för vårdpersonal att öva på viktiga procedurer och finslipa tekniker genom upprepad träning i en säker och kontrollerad miljö.
@@ -475,22 +976,71 @@
 Direkt feedback: Inbyggda sensorer mäter huvudposition, ET-tubplacering, navelkateter (UVC) -djup, HLR-prestation och mer – vilket ger omedelbar återkoppling för effektiv inlärning.</t>
   </si>
   <si>
+    <t>Vi har glädjen att bjuda in dig till Nordic SUN 2026 i Köpenhamn den 3–4 november. Under två inspirerande dagar samlar vi kollegor och experter från hela Norden för att dela erfarenheter, lära av varandra och utforska hur simulering kan bidra till bättre vård och ökad patientsäkerhet.
+Årets tema fokuserar på kvalitetsförbättring inom hälso- och sjukvården. Tillsammans utforskar vi hur simulering kan användas som ett effektivt verktyg för att förbättra vårdkvalitet och patientsäkerhet.
+Detta tvådagarsevenemang arrangeras i samarbete med Københavns Professionshøjskolen.
+Program
+Som deltagare får du möjlighet att skräddarsy ditt eget program genom att välja fem av åtta interaktiva workshops. Antalet platser är begränsat, så vi rekommenderar tidig anmälan.
+Mer information om workshoparna finns i avsnittet Agenda i inbjudan
+Antalet platser är begränsat och fördelat mellan de deltagande länderna
+Deltagande
+Deltagaravgiften är 80 EUR per person (inkluderar middag den 3 november)
+Faktura skickas till organisationen tre veckor före evenemanget
+Resa och boende bekostas av deltagaren
+Boende
+Förhandsbokningar finns på flera hotell i centrala Köpenhamn, nära platsen för middagen den 3 november. Mer information finns via länken i inbjudan.
+Frågor
+Vid frågor kring evenemanget är du välkommen att kontakta din kundansvarige: 
+Per Olofsson 
+Katarina Hemminger 
+Marcus Lidin
+Vi ser fram emot två inspirerande dagar tillsammans med dig.
+Med vänliga hälsningar,
+Københavns Professionshøjskole &amp; Laerdal Medical Nordic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I en serie av 5 tillfällen kommer vi fram till sommaren att bjuda in till webinars med fokus på SimCapture. 
+I det första webinaret kommer fokus vara på hur du kan använda och arbeta med den data som du samlar in och i ett nästa steg hur detta kan användas för att förbereda utbildningar, öka patientsäkerheten och ge bättre resultat för studenterna. 
+Q&amp;A görs på Norska/Svenska.
+All produktinformation kommer ges på engelska. 
+Välkommen att registrera dig för din plats här nedan!
+</t>
+  </si>
+  <si>
     <t>Utforska Laerdals färdighetstränare</t>
   </si>
   <si>
     <t>Läs mer</t>
   </si>
   <si>
+    <t>Program och anmälan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrera dig här </t>
+  </si>
+  <si>
     <t>Bygg kompetanse, styrk tillit og reduser risiko med MamaAnne</t>
   </si>
   <si>
     <t>Vi introduserer SIMETRI for mer realistisk traumetrening</t>
   </si>
   <si>
+    <t xml:space="preserve">Er du interesert i å delta på Nordic SUN 2026? </t>
+  </si>
+  <si>
+    <t>Få mer ut av din trening med Nursing Anne Simulator</t>
+  </si>
+  <si>
     <t>Nå tilgjengelig i medium og mørk hudtone</t>
   </si>
   <si>
     <t>Forbered deg på traumebehandling i virkeligheten med SIMETRIs avanserte og tilpassbare simuleringsverktøy.</t>
+  </si>
+  <si>
+    <t>Meld sin interesse for å delta på årets nettverksmøte</t>
+  </si>
+  <si>
+    <t>New bariatric patient care solutions.</t>
   </si>
   <si>
     <t>Bygg kompetanse, styrk tillit og reduser risiko</t>
@@ -498,6 +1048,13 @@
   <si>
     <t>SIMETRI®
 En pålitelig partner innen traumetrening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ønsker du å delta på årets Simulation User Network?
+</t>
+  </si>
+  <si>
+    <t>Få mer læring ut av hver treningsøkt med Nursing Anne Simulator</t>
   </si>
   <si>
     <t xml:space="preserve">Når helsepersonell har tilgang til gode og relevante treningsverktøy, kan mødredødelighet i stor grad forebygges. MamaAnne er utviklet nettopp for dette formålet – et viktig hjelpemiddel i arbeidet med tryggere fødsler.
@@ -516,25 +1073,65 @@
 Enten du forbereder deg til militære, sivile eller katastrofeinnsatser, løfter SIMETRIs skalerbare verktøy effekten av din simuleringsbaserte opplæring.​</t>
   </si>
   <si>
+    <t>Simulation User Network (SUN) samler hvert år fagpersoner som jobber med simulering, for å dele erfaringer, lære av hverandre og videreutvikle praksis på tvers av landegrenser. 
+I år vil nettverksmøtet ha et tydelig fokus på Healthcare Quality Improvement (HQI).
+Gjennom forelesninger og workshops får du innsikt i hvordan simulering kan brukes som en drivkraft for å forbedre kvalitet og pasientsikkerhet i helsetjenesten.
+Du vil møte kollegaer fra hele Norden, dele erfaringer og ta del i praktiske eksempler og faglige diskusjoner som gir deg nye perspektiver på hvordan simulering kan bidra til målbare forbedringer og varige endringer i klinisk praksis og utdanning.
+3.-4. November 2026 |  Københavns Professonshøjskole
+Årets arrangement organiseres av våre danske kollegaer, og det er et begrenset antall plasser som fordeles mellom de nordiske landene.
+Vi ønsker derfor å få en oversikt over interessen fra Norge.
+Ved å melde din interesse er du ikke garantert plass, men det gir oss et bedre grunnlag for fordeling dersom etterspørselen er stor. Deltakeravgiften er 80 €, inkludert middag tirsdag kveld.</t>
+  </si>
+  <si>
+    <t>Dere bruker allerede Nursing Anne Simulator til realistisk og effektiv ferdighetstrening. Med SimCapture Mobile Camera kan dere bygge videre på dette og skape enda bedre læringsopplevelser med økt fleksibilitet, bedre oversikt og større læringsutbytte.
+SimCapture Mobile Camera gjør en vanlig mobiltelefon eller et nettbrett om til et komplett opptaks- og strømmesystem – helt uten ekstra utstyr. Det betyr at dere enkelt kan filme og dokumentere scenarioer, transporttrening og in-situ-øvelser, akkurat der treningen faktisk foregår.
+Video gir et verdifullt grunnlag for refleksjon og debrief og styrker læringen for både instruktører og deltakere. SimCapture Mobile Camera kompletterer Nursing Anne Simulator og bidrar til mer realistisk, effektiv og engasjerende trening.</t>
+  </si>
+  <si>
     <t>Se videon og lær mer om  MamaAnne</t>
   </si>
   <si>
     <t>Utforsk mer</t>
   </si>
   <si>
+    <t>Klikk her for å melde din interesse</t>
+  </si>
+  <si>
+    <t>Les mer om SimCapture Mobile Camera</t>
+  </si>
+  <si>
     <t>지금 바로 SimCapture를 사용해 훈련의 새로운 가능성을 경험해 보세요.</t>
   </si>
   <si>
     <t xml:space="preserve">신생아 시뮬레이터 Emily와 Emma를 만나보세요! </t>
   </si>
   <si>
+    <t>[국제안전보건전시회] Laerdal Medical 부스를 찾아주셔서 감사합니다</t>
+  </si>
+  <si>
+    <t>[래어달메디컬코리아] 부산·울산·경남 지역 한정! 시뮬레이션 솔루션 정기 점검 프로모션</t>
+  </si>
+  <si>
     <t>AI로 강화된 강력한 시뮬레이션 관리 플랫폼으로 당신의 시뮬레이션 경험을 한층 더 향상시키세요.</t>
   </si>
   <si>
     <t>에밀리와 엠마로 신생아 시뮬레이션의 현실감을 높이고 맞춤화하세요.</t>
   </si>
   <si>
+    <t>산업현장에 필요한 Laerdal CPR 교육 솔루션, 지금 만나보세요!</t>
+  </si>
+  <si>
+    <t>본 프로모션은 기간 한정으로 조기에 일정이 마감될 수 있으므로, 참여를 원하시는 기관께서는 원활한 참여를 위해 빠른 신청 부탁드립니다.</t>
+  </si>
+  <si>
     <t>SimCapture로 시뮬레이션을 한 단계 더 발전시키세요</t>
+  </si>
+  <si>
+    <t>현장을 바꾸는 교육, 생명을 지키는 훈련</t>
+  </si>
+  <si>
+    <t>시뮬레이션 솔루션 정기 점검 프로모션 
+래어달메디컬코리아 공식대리점 제공 혜택</t>
   </si>
   <si>
     <t>훈련의 효과를 높이고 싶으신가요? SimCapture는 시뮬레이션 관리, 녹화, 피드백, 평가 과정을 간소화하는 강력한 플랫폼입니다. 직관적인 인터페이스를 통해 운영을 효율적으로 관리할 수 있으며, 강사와 참가자 모두에게 더 나은 결과를 제공합니다. 이 모든 기능을 한 곳에서 누려보세요.
@@ -561,19 +1158,61 @@
 </t>
   </si>
   <si>
+    <t>안녕하세요. 
+래어달메디컬코리아입니다. 
+이번 국제안전보건전시회 기간 중 래어달 부스를 방문해주시고, 저희 솔루션에 관심을 가져주셔서 진심으로 감사드립니다. 래어달은 "Helping save lives"라는 사명을 바탕으로, 실직적인 현장 교육과 대응 역량 강화를 위한 다양한 교육 및 훈련 솔루션을 제공하고 있습니다. 
+이번 전시회에서는 특히 산업 현장에서 유용하게 활용할 수 있는 일반인 대상 CPR 솔루션 제품을 중심으로 소개 드렸습니다. 보다 자세한 내용을 확인하실 수 있도록 주요 제품 정보 소개자료를 함께 보내드립니다. 
+Laerdal의 솔루션이 귀사의 안전 교육에 작은 도움이 되기를 바랍니다. 
+혹시 더 궁금하신 점이나, 실제 제품 데모 및 미팅이 필요하신 경우에는 언제든 편하게 회신 부탁드립니다. 고객의 니즈에 맞는 방향으로 함께 고민하고, 최적의 솔루션을 제안드릴 수 있도록 노력하겠습니다. 
+래어달메디컬코리아 드림</t>
+  </si>
+  <si>
+    <t>안녕하세요. 
+래어달메디컬코리아입니다. 
+부산·울산·경남지역 고객 여러분께 감사의 마음을 담아, 사용 중이신 시뮬레이션 솔루션에 대한 정기 점검 프로모션을 진행합니다. 
+자세한 내용은 아래 개요 및 첨부된 공문을 통해 확인해 주시기 바랍니다. 본 프로모션은 기간 한정으로 조기에 일정이 마감될 수 있으므로, 참여를 원하시는 기관께서는 원활한 참여를 위해 빠른 신청 부탁드립니다. 감사합니다.
+정기 점검 프로모션 개요
+대상: 부산, 울산, 경남지역 내 의료시뮬레이션 사용기관
+기간: 2025년 9월 1일~2025년 12월 31일
+목적:
+정기 점검 및 업그레이드를 통한 서비스 품질 향상과 시뮬레이션 학습환경 개선
+공식대리점을 통한 정품 공급 및 본사 기준의 서비스 제공
+신청방법:
+아래 담당자를 통해 신청 및 관련문의</t>
+  </si>
+  <si>
     <t>더 알아보기</t>
   </si>
   <si>
+    <t>Community CPR 제품
+소개자료 다운로드</t>
+  </si>
+  <si>
+    <t>정기 점검 프로모션 공문</t>
+  </si>
+  <si>
     <t>【レールダルウェビナー】 ビデオディブリーフィングの効果とメリット</t>
   </si>
   <si>
     <t>QCPRトレーニングがもっと便利に：新機能のご紹介</t>
   </si>
   <si>
+    <t>臨床現場を想定した男性患者対応演習に｜男性モデルのご紹介｜レールダル</t>
+  </si>
+  <si>
+    <t>【レールダルウェビナー】コンピテンシー基盤型教育の実践</t>
+  </si>
+  <si>
     <t>ビデオディブリーフィングでシミュレーション教育効果を高めましょう！</t>
   </si>
   <si>
     <t>レールダルのQCPRソリューションがさらに進化しました</t>
+  </si>
+  <si>
+    <t>ナーシングアンシミュレータ男性モデルのご紹介</t>
+  </si>
+  <si>
+    <t>看護大学教員を対象としたウェビナー（録画配信）です</t>
   </si>
   <si>
     <t>オンデマンド配信ウェビナーのご案内
@@ -582,6 +1221,13 @@
   <si>
     <t>QCPRソリューションが
 さらに進化しました</t>
+  </si>
+  <si>
+    <t>臨床現場を想定した男性患者対応演習に</t>
+  </si>
+  <si>
+    <t>レールダル ウェビナー録画配信のご案内
+コンピテンシー基盤型教育の実践</t>
   </si>
   <si>
     <t>本ウェビナーでは、シミュレーショントレーニングにおける動画活用の事例を紹介し、コンピテンシー評価や教育成果の向上にどう有効であるかについて、以下の点を中心に説明しています。
@@ -605,22 +1251,65 @@
 ぜひこの機会にログインして、新機能をご体験いただき、レールダル製品の可能性を最大限にご活用ください。</t>
   </si>
   <si>
+    <t>平素より弊社製品をご利用いただき、誠にありがとうございます。
+本メールでは、看護教育における学習シナリオの幅を広げ、多様な患者対応の実践力向上を支援する ナーシングアンシミュレータ「男性モデル」をご紹介いたします。
+日々様々な患者対応が求められる臨床現場において、男性患者を想定したトレーニングを取り入れることで、実際の看護場面に即した実践的なトレーニングが可能となります。
+本モデルは、異性対応を含む様々なケースを想定した演習に対応し、新人看護師教育や継続教育における現場対応力の向上に貢献します。
+院内研修や教育プログラムの充実をご検討の際にぜひご活用ください。
+製品の詳細や導入に関するご相談は、以下よりお気軽にお問い合わせください。
+以下の画像をクリックいただくと弊社ホームページ上にて製品の詳細をご覧いただけます。
+男性患者を想定したトレーニングに対応するナーシングアンシミュレータ男性モデル。
+これまで限られていた男性モデルでの演習を可能にし、看護教育の幅を広げます。
+ナーシングアンシミュレータは、老年モデル・女性モデル・男性モデルをラインアップ。
+学習目的やシナリオに応じて、柔軟に使い分けることが可能です。
+さらに質の高いシミュレーション教育を実現するためのソリューション
+シミュレーション録画システム：SimCaptureモバイルカメラ
+・トレーニングの映像記録を簡単に実現
+・研修の振り返りや教育記録として活用でき、効果的な学習を促進
+製品の詳細についてご質問やご要望などございましたら、以下のインサイドセールスまでお問い合わせください。
+配信解除については、下記「配信停止」よりお手続きをお願いいたします。</t>
+  </si>
+  <si>
+    <t>平素は格別のご高配を賜り、誠にありがとうございます。
+このたび弊社では、看護大学の教員の皆様を対象に開催し、大変ご好評をいただいた 2025年11月20日のウェビナーについて、録画配信としてあらためてご案内申し上げます。
+当ウェビナーでは、看護師養成課程における教育の質の向上を目的に、学生の臨床判断力や実践力を体系的に育成するための科目・授業設計の具体的な方法についてご紹介しております。
+教育カリキュラムの見直しをご検討中の方や、実践的な教育手法に関心のある方にぜひご参加いただきたい内容となっております。
+前回（11月20日）ご参加いただけなかった方はもちろん、再度内容を確認されたい方にもご視聴いただけるよう、録画配信をご用意いたしました。視聴には事前参加登録が必要となりますので、この機会にぜひお申込みください。
+お誘い合わせのうえ、多くの皆様にご視聴いただけますと幸いです。
+開催日時 ： 2026年3月25日（水）17:00～17:55
+申込方法 ：ウェビナー録画配信登録ボタンをクリックして事前にご登録ください
+参 加 費　: 無料
+演者および講演タイトルのご紹介
+コンピテンシー基盤型教育に基づく科目・授業設計
+～ シミュレーション教育導入と学修成果評価の具体的な方法 ～
+看護学教育モデル・コア・カリキュラム（令和6年度改訂版）は、卒業時に求められる資質・能力が体系化され、コンピテンシー基盤型教育（CBE）の転換が急務となった。講演では、CBEの科目・授業設計、シミュレーション教育によるコンピテンシー評価、段階的な学修方法について説明する。また、Millerのピラミッド「模擬的な環境下で行動・実演できる：shows how」の学修成果の評価ツールとしてのシミュレーションなどの実践も共有する。</t>
+  </si>
+  <si>
     <t>お問い合わせ</t>
   </si>
   <si>
     <t>最新情報はこちら</t>
   </si>
   <si>
+    <t>ウェビナー録画配信登録はこちら</t>
+  </si>
+  <si>
     <t>探索挪度QCPR应用程序的专业功能</t>
   </si>
   <si>
     <t>好消息！Emily 隆重上市</t>
   </si>
   <si>
+    <t>Virtual SUN | 医学精准教育中的模拟价值</t>
+  </si>
+  <si>
     <t>助力培训升级，无需额外费用。</t>
   </si>
   <si>
     <t>提升模拟真实感，定制新生儿培训体验。</t>
+  </si>
+  <si>
+    <t>5月28日19:00，线上见！</t>
   </si>
   <si>
     <t>挪度QCPR解决方案
@@ -628,6 +1317,11 @@
   </si>
   <si>
     <t>Emily 隆重上市</t>
+  </si>
+  <si>
+    <t>第三期 | 2026 Virtual SUN
+从“千人一面”到“因材施教”
+——医学精准教育中的模拟价值</t>
   </si>
   <si>
     <t>很高兴通知您，我们的QCPR解决方案再做强势升级——专业版功能全新上线，让培训更智能、更高效。您可以即刻免费解锁这些强大的新功能，为培训注入新活力。​
@@ -646,17 +1340,52 @@
 实时反馈：传感器可追踪头部倾斜角度、气管插管位置、脐静脉导管置入深度、心肺复苏表现等，为学员提供即时、可行的反馈。 </t>
   </si>
   <si>
+    <t>SUN（模拟用户交流会）以学术交流为主旨，聚焦探讨模拟教学如何提升患者安全、优化课程设计、培养师资队伍。从线下年度盛会到线上每月更新，我们期待以学术会友，助您碎片化学习、连接思想、启迪实践。
+活动信息：
+日期：5月28日（周四）
+时间：19:00-20:00
+平台：「挪度医疗」微信视频号
+本期看点：
+CBME推行多年，数据过载、反馈滞后如何破局？本期聚焦PME范式，看模拟技术如何让教育从“千人一面”走向“因材施教”：
+PME是什么？不止于个性化学习，而是一种系统化、数据驱动的教育新范式，致力于在正确的时间为正确的学习者提供正确的教育干预。
+P4框架如何落地？主动性、个性化、参与性、预测性——四大原则重塑医学教育路径。
+模拟为何是PME的理想实践场？从多模态学习分析到闭环反馈系统，AI如何驱动个性化干预？
+机遇与挑战并存：人工智能的应用潜力，以及需要警惕的数据偏见、伦理风险与实施陷阱。
+欢迎提前预约，一同探寻PME如何重塑未来医学人才培养！</t>
+  </si>
+  <si>
     <t>探索新功能</t>
   </si>
   <si>
     <t>了解更多</t>
+  </si>
+  <si>
+    <t>微信扫码 预约直播</t>
+  </si>
+  <si>
+    <t>Emily 助力提升新生儿培训水平</t>
+  </si>
+  <si>
+    <t>让您的团队从容应对各种新生儿紧急情况。</t>
+  </si>
+  <si>
+    <t>每个珍贵生命都值得最专业的呵护</t>
+  </si>
+  <si>
+    <t>我们期望每一次分娩都能如预期般顺利，但这不影响每个医护团队提前做好万全准备。
+我们最新的新生儿模拟人 Emily，有助于确保每个宝宝获得最好的生命开端，让团队能够以精湛的技能和十足的信心从容应对可能的挑战。
+凭借逼真的解剖结构、真实的新生儿特定病理场景以及智能反馈系统，Emily 将真实世界的复杂性融入每一个场景——无论是在医院还是在课堂。
+最脆弱的宝宝需要最关键的帮助。赋能您的团队，让他们在关键时刻为最脆弱的生命提供卓越的支持。</t>
+  </si>
+  <si>
+    <t>推进新生儿培训</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -677,23 +1406,17 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -708,22 +1431,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1058,77 +1789,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F760B220-41A1-4F5E-A962-C04D34A55F08}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="70.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="75" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="70.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="45.75">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="60.75">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="91.5">
-      <c r="A4" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="409.6">
-      <c r="A5" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>16</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1137,77 +1902,112 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB2F5F3F-6B5D-48ED-80CB-07B1A1D4A861}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E039F2-C569-465E-874E-09EACB151D86}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="64" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="65.140625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="64" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="30.75">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="45.75">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="275.25">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>107</v>
+      <c r="B4" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -1216,77 +2016,112 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64EE33F4-38E9-4FF0-8D25-E5B0330DB857}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB2F5F3F-6B5D-48ED-80CB-07B1A1D4A861}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="61.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="70" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="61.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="30.75">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="45.75">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="45.75">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="396.75">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>117</v>
+      <c r="B4" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -1295,77 +2130,112 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC2A3DC0-4FE5-488A-9C7F-FF67717077A4}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64EE33F4-38E9-4FF0-8D25-E5B0330DB857}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="63.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="69.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="66" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="63.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="34.5">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="34.5">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="33">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="409.6">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>125</v>
+      <c r="B4" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="390" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -1374,77 +2244,112 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF12633-665E-4FB2-BE9F-90DE50827076}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC2A3DC0-4FE5-488A-9C7F-FF67717077A4}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="66.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="70.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="66.5703125" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="66.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="33">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="33">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="33">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="409.6">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>135</v>
+      <c r="B4" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -1453,77 +2358,224 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF12633-665E-4FB2-BE9F-90DE50827076}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="71.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="65" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="71.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="33">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="33">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="409.6">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>145</v>
+      <c r="B4" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="66" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="66" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="375" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -1534,81 +2586,109 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E715CBA1-F5FD-4297-A14A-52EB4CBC3D57}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="79.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="79.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="67.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="12.140625" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="79.28515625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="18.75">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="285" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="45.75">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30.75">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="259.5">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>27</v>
+      <c r="B6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1617,78 +2697,112 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80B1E51-F154-48E2-ACAA-5AA9BDCF0760}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{786A2DE6-A3C8-471A-8E13-5713883C8915}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="70" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="104.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="98.140625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="70" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="30.75">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="45.75">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="396.75">
-      <c r="A5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>37</v>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="360" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1697,78 +2811,112 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F8DAEED-B4FF-4451-93AB-3B4058A07C66}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80B1E51-F154-48E2-ACAA-5AA9BDCF0760}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="76" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="104.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="98.140625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="76" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="45.75">
-      <c r="A2" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="45.75">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="396.75">
-      <c r="A5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>47</v>
+      <c r="B4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1777,77 +2925,112 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A59D234-95E3-474F-8A72-9FED2058BFDD}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F8DAEED-B4FF-4451-93AB-3B4058A07C66}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="85.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="77.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="76.85546875" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="85.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="30.75">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="45.75">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30.75">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="351">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>57</v>
+      <c r="B4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1856,77 +3039,111 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8864C6-84D4-4793-9B43-FD0AAA1064FB}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A59D234-95E3-474F-8A72-9FED2058BFDD}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="65.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65" style="2" customWidth="1"/>
-    <col min="3" max="3" width="60.28515625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="65.28515625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="30.75">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="45.75">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30.75">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="336">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>67</v>
+      <c r="B4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1935,77 +3152,111 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F01143B-74E6-4414-93D1-DEC938B822D6}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8864C6-84D4-4793-9B43-FD0AAA1064FB}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="63.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="81.28515625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="63.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="30.75">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30.75">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="409.6">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>77</v>
+      <c r="B4" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2014,77 +3265,112 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC1C9EA1-85D3-41E5-B529-631AE0E2F60F}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F01143B-74E6-4414-93D1-DEC938B822D6}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="78.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.42578125" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="78.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="45.75">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="45.75">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="282" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>87</v>
+      <c r="B4" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2093,77 +3379,112 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E039F2-C569-465E-874E-09EACB151D86}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC1C9EA1-85D3-41E5-B529-631AE0E2F60F}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="72.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="63.7109375" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="72.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="30.75">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="321">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>97</v>
+      <c r="B4" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="282" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
